--- a/assets/downloads/tables/lineage_names_2026-03-23.xlsx
+++ b/assets/downloads/tables/lineage_names_2026-03-23.xlsx
@@ -11225,7 +11225,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>L_COHEL_01        </t>
+          <t>L_COHEL_01</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
